--- a/apps/static/uploads/pupils_template.xlsx
+++ b/apps/static/uploads/pupils_template.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JJ\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\isiah\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719AFE2B-280E-4D9E-A383-0FB3F520598C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A43C20-7277-49CD-99F6-17FBC98B63AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pupils Template" sheetId="1" r:id="rId1"/>
-    <sheet name="drop_down_data" sheetId="2" r:id="rId2"/>
+    <sheet name="drop_down_data" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
   <si>
     <t>reg_no</t>
   </si>
@@ -35,6 +35,12 @@
     <t>last_name</t>
   </si>
   <si>
+    <t>nin_number</t>
+  </si>
+  <si>
+    <t>emis_number</t>
+  </si>
+  <si>
     <t>date_of_birth</t>
   </si>
   <si>
@@ -50,6 +56,9 @@
     <t>study_year</t>
   </si>
   <si>
+    <t>home_district</t>
+  </si>
+  <si>
     <t>address</t>
   </si>
   <si>
@@ -71,37 +80,112 @@
     <t>notes</t>
   </si>
   <si>
+    <t>residential_status</t>
+  </si>
+  <si>
+    <t>REG123</t>
+  </si>
+  <si>
+    <t>CM12345678</t>
+  </si>
+  <si>
+    <t>EMIS001</t>
+  </si>
+  <si>
+    <t>2008-05-15</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>2020-02-01</t>
+  </si>
+  <si>
+    <t>Kampala</t>
+  </si>
+  <si>
+    <t>123 Main St</t>
+  </si>
+  <si>
+    <t>0700000000</t>
+  </si>
+  <si>
+    <t>Above average</t>
+  </si>
+  <si>
+    <t>No notes</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
     <t>classes</t>
   </si>
   <si>
+    <t>BABY CLASS</t>
+  </si>
+  <si>
+    <t>MIDDLE</t>
+  </si>
+  <si>
+    <t>P7 Joint class 2025</t>
+  </si>
+  <si>
+    <t>PRIMARY 1</t>
+  </si>
+  <si>
+    <t>PRIMARY 2</t>
+  </si>
+  <si>
+    <t>PRIMARY 3</t>
+  </si>
+  <si>
+    <t>PRIMARY 4</t>
+  </si>
+  <si>
+    <t>PRIMARY 5</t>
+  </si>
+  <si>
+    <t>PRIMARY 6</t>
+  </si>
+  <si>
+    <t>PRIMARY 7</t>
+  </si>
+  <si>
+    <t>TOP CLASS</t>
+  </si>
+  <si>
     <t>study_years</t>
   </si>
   <si>
-    <t>mine, Primary 1</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>12min</t>
-  </si>
-  <si>
-    <t>zosh</t>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>2027</t>
+  </si>
+  <si>
+    <t>residential_statuses</t>
+  </si>
+  <si>
+    <t>Boarding</t>
+  </si>
+  <si>
+    <t>genders</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>isiah</t>
+  </si>
+  <si>
+    <t>walusimbi</t>
   </si>
   <si>
     <t>mine</t>
-  </si>
-  <si>
-    <t>gaka</t>
-  </si>
-  <si>
-    <t>male</t>
-  </si>
-  <si>
-    <t>Primary 1</t>
-  </si>
-  <si>
-    <t>waka</t>
   </si>
   <si>
     <t>none</t>
@@ -143,9 +227,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -448,16 +531,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -506,43 +586,55 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
       <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="1">
-        <v>33219</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>24</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="1">
-        <v>46003</v>
-      </c>
-      <c r="I2">
-        <v>2025</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" t="s">
         <v>26</v>
-      </c>
-      <c r="K2">
-        <v>759623689</v>
-      </c>
-      <c r="L2" t="s">
-        <v>27</v>
       </c>
       <c r="M2" t="s">
         <v>27</v>
@@ -551,44 +643,136 @@
         <v>28</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="P2" t="s">
-        <v>27</v>
+        <v>55</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>56</v>
+      </c>
+      <c r="R2" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" t="s">
+        <v>30</v>
+      </c>
+      <c r="T2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="G2:G100" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"mine,Primary 1"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I100" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"2025"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+          <x14:formula1>
+            <xm:f>drop_down_data!$B$1:$Z$1</xm:f>
+          </x14:formula1>
+          <xm:sqref>I2:I99</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
+          <x14:formula1>
+            <xm:f>drop_down_data!$B$2:$Z$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>K2:K99</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
+          <x14:formula1>
+            <xm:f>drop_down_data!$B$3:$Z$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>T2:T99</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
+          <x14:formula1>
+            <xm:f>drop_down_data!$B$4:$Z$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>H2:H99</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>33</v>
+      </c>
+      <c r="C1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>45</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
